--- a/data/templates/sale_template_v3.xlsx
+++ b/data/templates/sale_template_v3.xlsx
@@ -1312,51 +1312,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1361160</colOff>
-      <row>7</row>
-      <rowOff>122760</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="0" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="1713600" cy="1713600"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1847,7 +1802,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
